--- a/docs/Test_Report/Spi/TestPlanExecutionReport_SPI.xlsx
+++ b/docs/Test_Report/Spi/TestPlanExecutionReport_SPI.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Test Strategy Compliance'!$A$1:$E$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Plan | Execution Report'!$A$1:$U$228</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Plan | Execution Report'!$A$1:$U$227</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -77,7 +77,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D3D3D3"/>
+        <fgColor rgb="000000FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -724,7 +724,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572,MCAL-29573</t>
+          <t>MCAL-30790,MCAL-30792</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2025-03-13 14:35:17.681635-05:00 CDT</t>
+          <t>2025-06-09 06:41:31.972089-05:00 CDT</t>
         </is>
       </c>
     </row>
@@ -806,27 +806,27 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -843,32 +843,32 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1028,32 +1028,32 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>226</t>
         </is>
       </c>
     </row>
@@ -1119,27 +1119,27 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>0%</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>1%</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="inlineStr">
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5">
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="7" t="inlineStr">
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -1453,7 +1453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U228"/>
+  <dimension ref="A1:U227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1589,12 +1589,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr"/>
@@ -1730,12 +1730,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1852,12 +1852,12 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
@@ -1871,12 +1871,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1993,12 +1993,12 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr"/>
@@ -2012,12 +2012,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr"/>
@@ -2153,12 +2153,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr"/>
@@ -2284,12 +2284,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr"/>
@@ -2415,12 +2415,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr"/>
@@ -2546,12 +2546,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr"/>
@@ -2677,12 +2677,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr"/>
@@ -2808,12 +2808,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr"/>
@@ -2939,12 +2939,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr"/>
@@ -3070,12 +3070,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr"/>
@@ -3201,12 +3201,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr"/>
@@ -3332,12 +3332,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25032,MCAL-25036,MCAL-25034,MCAL-25037,MCAL-25033,MCAL-25035,MCAL-28304</t>
+          <t>MCAL-25032,MCAL-25036,MCAL-25034,MCAL-25037,MCAL-28304,MCAL-25033,MCAL-25035</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -3444,12 +3444,12 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr"/>
@@ -3463,12 +3463,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -3575,12 +3575,12 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr"/>
@@ -3594,12 +3594,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr"/>
@@ -3726,12 +3726,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr"/>
@@ -3858,12 +3858,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr"/>
@@ -3990,12 +3990,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr"/>
@@ -4122,12 +4122,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr"/>
@@ -4254,12 +4254,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr"/>
@@ -4386,12 +4386,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -4499,12 +4499,12 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
@@ -4518,12 +4518,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr"/>
@@ -4650,12 +4650,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr"/>
@@ -4782,12 +4782,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr"/>
@@ -4914,12 +4914,12 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -5027,12 +5027,12 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr"/>
@@ -5046,12 +5046,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -5159,12 +5159,12 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr"/>
@@ -5178,12 +5178,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr"/>
@@ -5309,12 +5309,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -5421,12 +5421,12 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr"/>
@@ -5440,12 +5440,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr"/>
@@ -5571,12 +5571,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr"/>
@@ -5702,12 +5702,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr"/>
@@ -5833,12 +5833,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr"/>
@@ -5964,12 +5964,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -6076,12 +6076,12 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr"/>
@@ -6095,12 +6095,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr"/>
@@ -6226,12 +6226,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr"/>
@@ -6357,12 +6357,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr"/>
@@ -6488,12 +6488,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -6600,12 +6600,12 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr"/>
@@ -6619,12 +6619,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr"/>
@@ -6752,12 +6752,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr"/>
@@ -6885,12 +6885,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -6999,12 +6999,12 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
@@ -7018,12 +7018,12 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -7131,12 +7131,12 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr"/>
@@ -7150,12 +7150,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -7263,12 +7263,12 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr"/>
@@ -7282,12 +7282,12 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -7395,12 +7395,12 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr"/>
@@ -7414,12 +7414,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr"/>
@@ -7546,12 +7546,12 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -7659,12 +7659,12 @@
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr"/>
@@ -7678,12 +7678,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr"/>
@@ -7809,12 +7809,12 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -7921,12 +7921,12 @@
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr"/>
@@ -7940,12 +7940,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr"/>
@@ -8071,12 +8071,12 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -8183,12 +8183,12 @@
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr"/>
@@ -8202,12 +8202,12 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr"/>
@@ -8333,12 +8333,12 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr"/>
@@ -8466,12 +8466,12 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -8578,12 +8578,12 @@
       </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr"/>
@@ -8597,12 +8597,12 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr"/>
@@ -8728,12 +8728,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr"/>
@@ -8859,12 +8859,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr"/>
@@ -8990,12 +8990,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -9102,12 +9102,12 @@
       </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S58" s="3" t="inlineStr"/>
@@ -9121,12 +9121,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr"/>
@@ -9252,12 +9252,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -9365,12 +9365,12 @@
       </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr"/>
@@ -9384,12 +9384,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr"/>
@@ -9515,12 +9515,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -9627,12 +9627,12 @@
       </c>
       <c r="Q62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr"/>
@@ -9646,12 +9646,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="Q63" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R63" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S63" s="3" t="inlineStr"/>
@@ -9777,12 +9777,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -9889,12 +9889,12 @@
       </c>
       <c r="Q64" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr"/>
@@ -9908,12 +9908,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="Q65" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R65" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S65" s="3" t="inlineStr"/>
@@ -10039,12 +10039,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -10151,12 +10151,12 @@
       </c>
       <c r="Q66" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S66" s="3" t="inlineStr"/>
@@ -10170,12 +10170,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -10282,12 +10282,12 @@
       </c>
       <c r="Q67" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R67" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S67" s="3" t="inlineStr"/>
@@ -10301,12 +10301,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -10413,12 +10413,12 @@
       </c>
       <c r="Q68" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S68" s="3" t="inlineStr"/>
@@ -10432,12 +10432,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -10544,12 +10544,12 @@
       </c>
       <c r="Q69" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R69" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S69" s="3" t="inlineStr"/>
@@ -10563,12 +10563,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -10675,12 +10675,12 @@
       </c>
       <c r="Q70" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr"/>
@@ -10694,12 +10694,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -10806,12 +10806,12 @@
       </c>
       <c r="Q71" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr"/>
@@ -10825,12 +10825,12 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -10937,12 +10937,12 @@
       </c>
       <c r="Q72" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S72" s="3" t="inlineStr"/>
@@ -10956,12 +10956,12 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -11068,12 +11068,12 @@
       </c>
       <c r="Q73" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R73" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S73" s="3" t="inlineStr"/>
@@ -11087,12 +11087,12 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -11199,12 +11199,12 @@
       </c>
       <c r="Q74" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S74" s="3" t="inlineStr"/>
@@ -11218,12 +11218,12 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -11330,12 +11330,12 @@
       </c>
       <c r="Q75" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R75" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S75" s="3" t="inlineStr"/>
@@ -11349,12 +11349,12 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="Q76" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S76" s="3" t="inlineStr"/>
@@ -11480,12 +11480,12 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -11592,12 +11592,12 @@
       </c>
       <c r="Q77" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R77" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S77" s="3" t="inlineStr"/>
@@ -11611,12 +11611,12 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -11723,12 +11723,12 @@
       </c>
       <c r="Q78" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S78" s="3" t="inlineStr"/>
@@ -11742,12 +11742,12 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="Q79" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R79" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S79" s="3" t="inlineStr"/>
@@ -11873,12 +11873,12 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -11985,12 +11985,12 @@
       </c>
       <c r="Q80" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R80" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S80" s="3" t="inlineStr"/>
@@ -12004,12 +12004,12 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -12116,12 +12116,12 @@
       </c>
       <c r="Q81" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R81" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S81" s="3" t="inlineStr"/>
@@ -12135,12 +12135,12 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -12247,12 +12247,12 @@
       </c>
       <c r="Q82" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R82" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S82" s="3" t="inlineStr"/>
@@ -12266,12 +12266,12 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -12378,12 +12378,12 @@
       </c>
       <c r="Q83" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R83" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S83" s="3" t="inlineStr"/>
@@ -12397,12 +12397,12 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -12509,12 +12509,12 @@
       </c>
       <c r="Q84" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R84" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S84" s="3" t="inlineStr"/>
@@ -12528,12 +12528,12 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="Q85" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R85" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S85" s="3" t="inlineStr"/>
@@ -12659,12 +12659,12 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="Q86" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S86" s="3" t="inlineStr"/>
@@ -12790,12 +12790,12 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -12902,12 +12902,12 @@
       </c>
       <c r="Q87" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R87" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S87" s="3" t="inlineStr"/>
@@ -12921,12 +12921,12 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="Q88" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S88" s="3" t="inlineStr"/>
@@ -13052,12 +13052,12 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -13164,12 +13164,12 @@
       </c>
       <c r="Q89" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R89" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S89" s="3" t="inlineStr"/>
@@ -13183,12 +13183,12 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -13295,12 +13295,12 @@
       </c>
       <c r="Q90" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr"/>
@@ -13314,12 +13314,12 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -13426,12 +13426,12 @@
       </c>
       <c r="Q91" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R91" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S91" s="3" t="inlineStr"/>
@@ -13445,12 +13445,12 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -13557,12 +13557,12 @@
       </c>
       <c r="Q92" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R92" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S92" s="3" t="inlineStr"/>
@@ -13576,12 +13576,12 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -13688,12 +13688,12 @@
       </c>
       <c r="Q93" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R93" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S93" s="3" t="inlineStr"/>
@@ -13707,12 +13707,12 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -13819,12 +13819,12 @@
       </c>
       <c r="Q94" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R94" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S94" s="3" t="inlineStr"/>
@@ -13838,12 +13838,12 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -13950,12 +13950,12 @@
       </c>
       <c r="Q95" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R95" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S95" s="3" t="inlineStr"/>
@@ -13969,12 +13969,12 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -14081,12 +14081,12 @@
       </c>
       <c r="Q96" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R96" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S96" s="3" t="inlineStr"/>
@@ -14100,12 +14100,12 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="Q97" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R97" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S97" s="3" t="inlineStr"/>
@@ -14231,12 +14231,12 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -14343,12 +14343,12 @@
       </c>
       <c r="Q98" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S98" s="3" t="inlineStr"/>
@@ -14362,12 +14362,12 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25053,MCAL-25049,MCAL-28318,MCAL-28336,MCAL-28342,MCAL-28348,MCAL-25064,MCAL-25056,MCAL-25063,MCAL-25055,MCAL-28356,MCAL-28593,MCAL-25062,MCAL-25052,MCAL-25048,MCAL-28323,MCAL-28330,MCAL-28353,MCAL-28335</t>
+          <t>MCAL-25053,MCAL-25049,MCAL-28318,MCAL-28336,MCAL-28342,MCAL-28348,MCAL-25064,MCAL-25056,MCAL-25063,MCAL-25055,MCAL-28356,MCAL-28593,MCAL-25062,MCAL-25052,MCAL-25048,MCAL-28323,MCAL-28330,MCAL-28335,MCAL-28353</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -14474,12 +14474,12 @@
       </c>
       <c r="Q99" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R99" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S99" s="3" t="inlineStr"/>
@@ -14493,12 +14493,12 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28305,MCAL-28306,MCAL-28329,MCAL-28343,MCAL-28349,MCAL-28350,MCAL-25055,MCAL-25056,MCAL-25052,MCAL-25053,MCAL-25049,MCAL-28326,MCAL-28333,MCAL-25092,MCAL-25168,MCAL-28346,MCAL-28320,MCAL-28334,MCAL-28331,MCAL-28314,MCAL-28317,MCAL-28325,MCAL-28344,MCAL-28299,MCAL-28324,MCAL-28327,MCAL-28298,MCAL-28322,MCAL-28339,MCAL-28347,MCAL-25017,MCAL-25018,MCAL-25048,MCAL-28340,MCAL-28352,MCAL-28295,MCAL-24853,MCAL-28315,MCAL-28316,MCAL-28337,MCAL-28319,MCAL-28338,MCAL-28297,MCAL-28313,MCAL-28328,MCAL-28312,MCAL-28341,MCAL-28345</t>
+          <t>MCAL-28305,MCAL-28306,MCAL-28329,MCAL-28343,MCAL-28349,MCAL-28350,MCAL-25055,MCAL-25056,MCAL-25052,MCAL-25053,MCAL-25049,MCAL-28326,MCAL-28333,MCAL-25092,MCAL-25168,MCAL-28346,MCAL-28320,MCAL-28313,MCAL-28328,MCAL-28334,MCAL-28331,MCAL-28314,MCAL-28317,MCAL-28325,MCAL-28344,MCAL-28299,MCAL-28312,MCAL-28324,MCAL-28327,MCAL-28298,MCAL-28322,MCAL-28339,MCAL-28347,MCAL-28341,MCAL-28345,MCAL-25017,MCAL-25018,MCAL-25048,MCAL-28340,MCAL-28352,MCAL-28295,MCAL-24853,MCAL-28315,MCAL-28316,MCAL-28297,MCAL-28337,MCAL-28319,MCAL-28338</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -14605,12 +14605,12 @@
       </c>
       <c r="Q100" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R100" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S100" s="3" t="inlineStr"/>
@@ -14624,12 +14624,12 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -14736,12 +14736,12 @@
       </c>
       <c r="Q101" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R101" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S101" s="3" t="inlineStr"/>
@@ -14755,12 +14755,12 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -14868,12 +14868,12 @@
       </c>
       <c r="Q102" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R102" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S102" s="3" t="inlineStr"/>
@@ -14887,12 +14887,12 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -15000,12 +15000,12 @@
       </c>
       <c r="Q103" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R103" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S103" s="3" t="inlineStr"/>
@@ -15019,12 +15019,12 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -15132,12 +15132,12 @@
       </c>
       <c r="Q104" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R104" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S104" s="3" t="inlineStr"/>
@@ -15151,12 +15151,12 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="Q105" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R105" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S105" s="3" t="inlineStr"/>
@@ -15283,12 +15283,12 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -15395,12 +15395,12 @@
       </c>
       <c r="Q106" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R106" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S106" s="3" t="inlineStr"/>
@@ -15414,12 +15414,12 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -15526,12 +15526,12 @@
       </c>
       <c r="Q107" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R107" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S107" s="3" t="inlineStr"/>
@@ -15545,12 +15545,12 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -15570,7 +15570,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>MCAL-24994,MCAL-28289,MCAL-28294,MCAL-28309,MCAL-28351,MCAL-25163,MCAL-24985,MCAL-25179,MCAL-24992,MCAL-24961,MCAL-28355,MCAL-25176,MCAL-28311,MCAL-28321,MCAL-28308,MCAL-28290,MCAL-28288,MCAL-24995,MCAL-25164,MCAL-28310,MCAL-28300,MCAL-28307,MCAL-28332,MCAL-28354,MCAL-28293,MCAL-25174,MCAL-25165</t>
+          <t>MCAL-24994,MCAL-28289,MCAL-28294,MCAL-28309,MCAL-28351,MCAL-25163,MCAL-24985,MCAL-25179,MCAL-24992,MCAL-24961,MCAL-28355,MCAL-25176,MCAL-28311,MCAL-28321,MCAL-28308,MCAL-28290,MCAL-28288,MCAL-24995,MCAL-25164,MCAL-28310,MCAL-28300,MCAL-28307,MCAL-28332,MCAL-28354,MCAL-28293,MCAL-25165,MCAL-25174</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -15657,12 +15657,12 @@
       </c>
       <c r="Q108" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R108" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S108" s="3" t="inlineStr"/>
@@ -15676,12 +15676,12 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -15788,12 +15788,12 @@
       </c>
       <c r="Q109" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R109" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S109" s="3" t="inlineStr"/>
@@ -15807,12 +15807,12 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -15919,12 +15919,12 @@
       </c>
       <c r="Q110" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R110" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S110" s="3" t="inlineStr"/>
@@ -15938,12 +15938,12 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -16050,12 +16050,12 @@
       </c>
       <c r="Q111" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R111" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S111" s="3" t="inlineStr"/>
@@ -16069,12 +16069,12 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="Q112" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R112" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S112" s="3" t="inlineStr"/>
@@ -16200,12 +16200,12 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -16312,12 +16312,12 @@
       </c>
       <c r="Q113" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R113" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S113" s="3" t="inlineStr"/>
@@ -16331,12 +16331,12 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -16443,12 +16443,12 @@
       </c>
       <c r="Q114" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R114" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S114" s="3" t="inlineStr"/>
@@ -16462,12 +16462,12 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -16576,12 +16576,12 @@
       </c>
       <c r="Q115" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R115" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S115" s="3" t="inlineStr"/>
@@ -16595,12 +16595,12 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -16709,12 +16709,12 @@
       </c>
       <c r="Q116" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R116" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S116" s="3" t="inlineStr"/>
@@ -16728,12 +16728,12 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -16842,12 +16842,12 @@
       </c>
       <c r="Q117" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R117" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S117" s="3" t="inlineStr"/>
@@ -16861,12 +16861,12 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -16974,12 +16974,12 @@
       </c>
       <c r="Q118" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R118" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S118" s="3" t="inlineStr"/>
@@ -16993,12 +16993,12 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -17106,12 +17106,12 @@
       </c>
       <c r="Q119" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R119" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S119" s="3" t="inlineStr"/>
@@ -17125,12 +17125,12 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -17238,12 +17238,12 @@
       </c>
       <c r="Q120" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R120" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S120" s="3" t="inlineStr"/>
@@ -17257,12 +17257,12 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -17370,12 +17370,12 @@
       </c>
       <c r="Q121" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R121" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S121" s="3" t="inlineStr"/>
@@ -17389,12 +17389,12 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -17502,12 +17502,12 @@
       </c>
       <c r="Q122" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R122" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S122" s="3" t="inlineStr"/>
@@ -17521,12 +17521,12 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -17634,12 +17634,12 @@
       </c>
       <c r="Q123" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R123" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S123" s="3" t="inlineStr"/>
@@ -17653,12 +17653,12 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -17766,12 +17766,12 @@
       </c>
       <c r="Q124" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R124" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S124" s="3" t="inlineStr"/>
@@ -17785,12 +17785,12 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -17898,12 +17898,12 @@
       </c>
       <c r="Q125" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R125" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S125" s="3" t="inlineStr"/>
@@ -17917,12 +17917,12 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -18030,12 +18030,12 @@
       </c>
       <c r="Q126" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R126" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S126" s="3" t="inlineStr"/>
@@ -18049,12 +18049,12 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -18162,12 +18162,12 @@
       </c>
       <c r="Q127" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R127" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S127" s="3" t="inlineStr"/>
@@ -18181,12 +18181,12 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -18294,12 +18294,12 @@
       </c>
       <c r="Q128" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R128" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S128" s="3" t="inlineStr"/>
@@ -18313,12 +18313,12 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -18426,12 +18426,12 @@
       </c>
       <c r="Q129" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R129" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S129" s="3" t="inlineStr"/>
@@ -18445,12 +18445,12 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -18559,12 +18559,12 @@
       </c>
       <c r="Q130" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R130" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S130" s="3" t="inlineStr"/>
@@ -18578,12 +18578,12 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -18692,12 +18692,12 @@
       </c>
       <c r="Q131" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R131" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S131" s="3" t="inlineStr"/>
@@ -18711,12 +18711,12 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -18825,12 +18825,12 @@
       </c>
       <c r="Q132" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R132" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S132" s="3" t="inlineStr"/>
@@ -18844,12 +18844,12 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -18958,12 +18958,12 @@
       </c>
       <c r="Q133" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R133" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S133" s="3" t="inlineStr"/>
@@ -18977,12 +18977,12 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -19091,12 +19091,12 @@
       </c>
       <c r="Q134" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R134" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S134" s="3" t="inlineStr"/>
@@ -19110,12 +19110,12 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -19224,12 +19224,12 @@
       </c>
       <c r="Q135" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R135" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S135" s="3" t="inlineStr"/>
@@ -19243,12 +19243,12 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -19358,12 +19358,12 @@
       </c>
       <c r="Q136" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R136" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S136" s="3" t="inlineStr"/>
@@ -19377,12 +19377,12 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
@@ -19489,12 +19489,12 @@
       </c>
       <c r="Q137" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R137" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S137" s="3" t="inlineStr"/>
@@ -19508,12 +19508,12 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
@@ -19621,12 +19621,12 @@
       </c>
       <c r="Q138" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R138" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S138" s="3" t="inlineStr"/>
@@ -19640,12 +19640,12 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29570</t>
+          <t>MCAL-30789</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -19753,12 +19753,12 @@
       </c>
       <c r="Q139" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29572</t>
+          <t>MCAL-30790</t>
         </is>
       </c>
       <c r="R139" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S139" s="3" t="inlineStr"/>
@@ -19772,12 +19772,12 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -19852,31 +19852,31 @@
       </c>
       <c r="Q140" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R140" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S140" s="3" t="inlineStr"/>
       <c r="T140" s="3" t="inlineStr"/>
-      <c r="U140" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U140" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -19983,31 +19983,31 @@
       </c>
       <c r="Q141" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R141" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S141" s="3" t="inlineStr"/>
       <c r="T141" s="3" t="inlineStr"/>
-      <c r="U141" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U141" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -20089,31 +20089,31 @@
       </c>
       <c r="Q142" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R142" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S142" s="3" t="inlineStr"/>
       <c r="T142" s="3" t="inlineStr"/>
-      <c r="U142" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U142" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
@@ -20188,31 +20188,31 @@
       </c>
       <c r="Q143" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R143" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S143" s="3" t="inlineStr"/>
       <c r="T143" s="3" t="inlineStr"/>
-      <c r="U143" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U143" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -20287,31 +20287,31 @@
       </c>
       <c r="Q144" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R144" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S144" s="3" t="inlineStr"/>
       <c r="T144" s="3" t="inlineStr"/>
-      <c r="U144" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U144" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
@@ -20386,31 +20386,31 @@
       </c>
       <c r="Q145" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R145" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S145" s="3" t="inlineStr"/>
       <c r="T145" s="3" t="inlineStr"/>
-      <c r="U145" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U145" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -20485,31 +20485,31 @@
       </c>
       <c r="Q146" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R146" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S146" s="3" t="inlineStr"/>
       <c r="T146" s="3" t="inlineStr"/>
-      <c r="U146" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U146" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -20584,31 +20584,31 @@
       </c>
       <c r="Q147" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R147" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S147" s="3" t="inlineStr"/>
       <c r="T147" s="3" t="inlineStr"/>
-      <c r="U147" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U147" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -20683,31 +20683,31 @@
       </c>
       <c r="Q148" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R148" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S148" s="3" t="inlineStr"/>
       <c r="T148" s="3" t="inlineStr"/>
-      <c r="U148" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U148" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -20784,31 +20784,31 @@
       </c>
       <c r="Q149" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R149" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S149" s="3" t="inlineStr"/>
       <c r="T149" s="3" t="inlineStr"/>
-      <c r="U149" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U149" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -20883,31 +20883,31 @@
       </c>
       <c r="Q150" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R150" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S150" s="3" t="inlineStr"/>
       <c r="T150" s="3" t="inlineStr"/>
-      <c r="U150" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U150" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -20983,31 +20983,31 @@
       </c>
       <c r="Q151" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R151" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S151" s="3" t="inlineStr"/>
       <c r="T151" s="3" t="inlineStr"/>
-      <c r="U151" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U151" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -21084,31 +21084,31 @@
       </c>
       <c r="Q152" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R152" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S152" s="3" t="inlineStr"/>
       <c r="T152" s="3" t="inlineStr"/>
-      <c r="U152" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U152" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
@@ -21186,31 +21186,31 @@
       </c>
       <c r="Q153" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R153" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S153" s="3" t="inlineStr"/>
       <c r="T153" s="3" t="inlineStr"/>
-      <c r="U153" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U153" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -21293,31 +21293,31 @@
       </c>
       <c r="Q154" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R154" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S154" s="3" t="inlineStr"/>
       <c r="T154" s="3" t="inlineStr"/>
-      <c r="U154" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U154" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
@@ -21392,31 +21392,31 @@
       </c>
       <c r="Q155" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R155" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S155" s="3" t="inlineStr"/>
       <c r="T155" s="3" t="inlineStr"/>
-      <c r="U155" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U155" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -21491,31 +21491,31 @@
       </c>
       <c r="Q156" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R156" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S156" s="3" t="inlineStr"/>
       <c r="T156" s="3" t="inlineStr"/>
-      <c r="U156" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U156" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -21591,31 +21591,31 @@
       </c>
       <c r="Q157" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R157" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S157" s="3" t="inlineStr"/>
       <c r="T157" s="3" t="inlineStr"/>
-      <c r="U157" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U157" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -21696,31 +21696,31 @@
       </c>
       <c r="Q158" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R158" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S158" s="3" t="inlineStr"/>
       <c r="T158" s="3" t="inlineStr"/>
-      <c r="U158" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U158" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -21795,31 +21795,31 @@
       </c>
       <c r="Q159" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R159" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S159" s="3" t="inlineStr"/>
       <c r="T159" s="3" t="inlineStr"/>
-      <c r="U159" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U159" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -21926,31 +21926,31 @@
       </c>
       <c r="Q160" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R160" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S160" s="3" t="inlineStr"/>
       <c r="T160" s="3" t="inlineStr"/>
-      <c r="U160" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U160" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -22057,31 +22057,31 @@
       </c>
       <c r="Q161" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R161" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S161" s="3" t="inlineStr"/>
       <c r="T161" s="3" t="inlineStr"/>
-      <c r="U161" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U161" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
@@ -22188,31 +22188,31 @@
       </c>
       <c r="Q162" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R162" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S162" s="3" t="inlineStr"/>
       <c r="T162" s="3" t="inlineStr"/>
-      <c r="U162" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U162" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -22319,31 +22319,31 @@
       </c>
       <c r="Q163" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R163" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S163" s="3" t="inlineStr"/>
       <c r="T163" s="3" t="inlineStr"/>
-      <c r="U163" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U163" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -22450,31 +22450,31 @@
       </c>
       <c r="Q164" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R164" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S164" s="3" t="inlineStr"/>
       <c r="T164" s="3" t="inlineStr"/>
-      <c r="U164" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U164" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
@@ -22581,31 +22581,31 @@
       </c>
       <c r="Q165" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R165" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S165" s="3" t="inlineStr"/>
       <c r="T165" s="3" t="inlineStr"/>
-      <c r="U165" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U165" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -22680,31 +22680,31 @@
       </c>
       <c r="Q166" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R166" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S166" s="3" t="inlineStr"/>
       <c r="T166" s="3" t="inlineStr"/>
-      <c r="U166" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U166" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
@@ -22782,31 +22782,31 @@
       </c>
       <c r="Q167" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R167" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S167" s="3" t="inlineStr"/>
       <c r="T167" s="3" t="inlineStr"/>
-      <c r="U167" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U167" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -22881,31 +22881,31 @@
       </c>
       <c r="Q168" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R168" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S168" s="3" t="inlineStr"/>
       <c r="T168" s="3" t="inlineStr"/>
-      <c r="U168" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U168" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
@@ -23013,31 +23013,31 @@
       </c>
       <c r="Q169" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R169" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S169" s="3" t="inlineStr"/>
       <c r="T169" s="3" t="inlineStr"/>
-      <c r="U169" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U169" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -23145,31 +23145,31 @@
       </c>
       <c r="Q170" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R170" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S170" s="3" t="inlineStr"/>
       <c r="T170" s="3" t="inlineStr"/>
       <c r="U170" s="11" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
@@ -23244,31 +23244,31 @@
       </c>
       <c r="Q171" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R171" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S171" s="3" t="inlineStr"/>
       <c r="T171" s="3" t="inlineStr"/>
-      <c r="U171" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U171" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
@@ -23375,31 +23375,31 @@
       </c>
       <c r="Q172" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R172" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S172" s="3" t="inlineStr"/>
       <c r="T172" s="3" t="inlineStr"/>
-      <c r="U172" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U172" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
@@ -23474,31 +23474,31 @@
       </c>
       <c r="Q173" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R173" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S173" s="3" t="inlineStr"/>
       <c r="T173" s="3" t="inlineStr"/>
-      <c r="U173" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U173" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
@@ -23574,31 +23574,31 @@
       </c>
       <c r="Q174" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R174" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S174" s="3" t="inlineStr"/>
       <c r="T174" s="3" t="inlineStr"/>
-      <c r="U174" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U174" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
@@ -23675,31 +23675,31 @@
       </c>
       <c r="Q175" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R175" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S175" s="3" t="inlineStr"/>
       <c r="T175" s="3" t="inlineStr"/>
-      <c r="U175" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U175" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
@@ -23775,31 +23775,31 @@
       </c>
       <c r="Q176" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R176" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S176" s="3" t="inlineStr"/>
       <c r="T176" s="3" t="inlineStr"/>
-      <c r="U176" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U176" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
@@ -23875,31 +23875,31 @@
       </c>
       <c r="Q177" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R177" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S177" s="3" t="inlineStr"/>
       <c r="T177" s="3" t="inlineStr"/>
-      <c r="U177" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U177" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -23974,31 +23974,31 @@
       </c>
       <c r="Q178" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R178" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S178" s="3" t="inlineStr"/>
       <c r="T178" s="3" t="inlineStr"/>
-      <c r="U178" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U178" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
@@ -24074,31 +24074,31 @@
       </c>
       <c r="Q179" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R179" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S179" s="3" t="inlineStr"/>
       <c r="T179" s="3" t="inlineStr"/>
-      <c r="U179" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U179" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
@@ -24175,31 +24175,31 @@
       </c>
       <c r="Q180" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R180" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S180" s="3" t="inlineStr"/>
       <c r="T180" s="3" t="inlineStr"/>
-      <c r="U180" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U180" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
@@ -24275,31 +24275,31 @@
       </c>
       <c r="Q181" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R181" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S181" s="3" t="inlineStr"/>
       <c r="T181" s="3" t="inlineStr"/>
-      <c r="U181" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U181" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -24374,31 +24374,31 @@
       </c>
       <c r="Q182" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R182" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S182" s="3" t="inlineStr"/>
       <c r="T182" s="3" t="inlineStr"/>
-      <c r="U182" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U182" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
@@ -24474,31 +24474,31 @@
       </c>
       <c r="Q183" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R183" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S183" s="3" t="inlineStr"/>
       <c r="T183" s="3" t="inlineStr"/>
-      <c r="U183" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U183" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -24574,31 +24574,31 @@
       </c>
       <c r="Q184" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R184" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S184" s="3" t="inlineStr"/>
       <c r="T184" s="3" t="inlineStr"/>
-      <c r="U184" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U184" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -24675,31 +24675,31 @@
       </c>
       <c r="Q185" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R185" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S185" s="3" t="inlineStr"/>
       <c r="T185" s="3" t="inlineStr"/>
-      <c r="U185" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U185" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -24776,31 +24776,31 @@
       </c>
       <c r="Q186" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R186" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S186" s="3" t="inlineStr"/>
       <c r="T186" s="3" t="inlineStr"/>
-      <c r="U186" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U186" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
@@ -24875,31 +24875,31 @@
       </c>
       <c r="Q187" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R187" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S187" s="3" t="inlineStr"/>
       <c r="T187" s="3" t="inlineStr"/>
-      <c r="U187" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U187" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
@@ -24975,31 +24975,31 @@
       </c>
       <c r="Q188" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R188" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S188" s="3" t="inlineStr"/>
       <c r="T188" s="3" t="inlineStr"/>
-      <c r="U188" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U188" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
@@ -25106,31 +25106,31 @@
       </c>
       <c r="Q189" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R189" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S189" s="3" t="inlineStr"/>
       <c r="T189" s="3" t="inlineStr"/>
-      <c r="U189" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U189" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -25206,31 +25206,31 @@
       </c>
       <c r="Q190" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R190" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S190" s="3" t="inlineStr"/>
       <c r="T190" s="3" t="inlineStr"/>
-      <c r="U190" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U190" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
@@ -25306,31 +25306,31 @@
       </c>
       <c r="Q191" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R191" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S191" s="3" t="inlineStr"/>
       <c r="T191" s="3" t="inlineStr"/>
-      <c r="U191" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U191" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -25405,31 +25405,31 @@
       </c>
       <c r="Q192" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R192" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S192" s="3" t="inlineStr"/>
       <c r="T192" s="3" t="inlineStr"/>
-      <c r="U192" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U192" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
@@ -25504,31 +25504,31 @@
       </c>
       <c r="Q193" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R193" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S193" s="3" t="inlineStr"/>
       <c r="T193" s="3" t="inlineStr"/>
-      <c r="U193" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U193" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
@@ -25603,31 +25603,31 @@
       </c>
       <c r="Q194" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R194" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S194" s="3" t="inlineStr"/>
       <c r="T194" s="3" t="inlineStr"/>
-      <c r="U194" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U194" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
@@ -25702,31 +25702,31 @@
       </c>
       <c r="Q195" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R195" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S195" s="3" t="inlineStr"/>
       <c r="T195" s="3" t="inlineStr"/>
-      <c r="U195" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U195" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
@@ -25801,31 +25801,31 @@
       </c>
       <c r="Q196" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R196" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S196" s="3" t="inlineStr"/>
       <c r="T196" s="3" t="inlineStr"/>
-      <c r="U196" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U196" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
@@ -25900,31 +25900,31 @@
       </c>
       <c r="Q197" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R197" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S197" s="3" t="inlineStr"/>
       <c r="T197" s="3" t="inlineStr"/>
-      <c r="U197" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U197" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
@@ -25999,31 +25999,31 @@
       </c>
       <c r="Q198" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R198" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S198" s="3" t="inlineStr"/>
       <c r="T198" s="3" t="inlineStr"/>
-      <c r="U198" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U198" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
@@ -26098,31 +26098,31 @@
       </c>
       <c r="Q199" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R199" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S199" s="3" t="inlineStr"/>
       <c r="T199" s="3" t="inlineStr"/>
-      <c r="U199" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U199" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
@@ -26197,31 +26197,31 @@
       </c>
       <c r="Q200" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R200" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S200" s="3" t="inlineStr"/>
       <c r="T200" s="3" t="inlineStr"/>
-      <c r="U200" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U200" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
@@ -26296,31 +26296,31 @@
       </c>
       <c r="Q201" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R201" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S201" s="3" t="inlineStr"/>
       <c r="T201" s="3" t="inlineStr"/>
-      <c r="U201" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U201" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
@@ -26395,31 +26395,31 @@
       </c>
       <c r="Q202" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R202" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S202" s="3" t="inlineStr"/>
       <c r="T202" s="3" t="inlineStr"/>
-      <c r="U202" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U202" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
@@ -26526,31 +26526,31 @@
       </c>
       <c r="Q203" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R203" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S203" s="3" t="inlineStr"/>
       <c r="T203" s="3" t="inlineStr"/>
-      <c r="U203" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U203" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
@@ -26658,31 +26658,31 @@
       </c>
       <c r="Q204" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R204" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S204" s="3" t="inlineStr"/>
       <c r="T204" s="3" t="inlineStr"/>
-      <c r="U204" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U204" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
@@ -26790,31 +26790,31 @@
       </c>
       <c r="Q205" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R205" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S205" s="3" t="inlineStr"/>
       <c r="T205" s="3" t="inlineStr"/>
       <c r="U205" s="11" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
@@ -26921,31 +26921,31 @@
       </c>
       <c r="Q206" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R206" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S206" s="3" t="inlineStr"/>
       <c r="T206" s="3" t="inlineStr"/>
-      <c r="U206" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U206" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
@@ -27052,31 +27052,31 @@
       </c>
       <c r="Q207" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R207" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S207" s="3" t="inlineStr"/>
       <c r="T207" s="3" t="inlineStr"/>
-      <c r="U207" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U207" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
@@ -27183,31 +27183,31 @@
       </c>
       <c r="Q208" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R208" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S208" s="3" t="inlineStr"/>
       <c r="T208" s="3" t="inlineStr"/>
-      <c r="U208" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U208" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
@@ -27282,31 +27282,31 @@
       </c>
       <c r="Q209" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R209" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S209" s="3" t="inlineStr"/>
       <c r="T209" s="3" t="inlineStr"/>
-      <c r="U209" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U209" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
@@ -27381,31 +27381,31 @@
       </c>
       <c r="Q210" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R210" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S210" s="3" t="inlineStr"/>
       <c r="T210" s="3" t="inlineStr"/>
-      <c r="U210" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U210" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
@@ -27480,31 +27480,31 @@
       </c>
       <c r="Q211" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R211" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S211" s="3" t="inlineStr"/>
       <c r="T211" s="3" t="inlineStr"/>
-      <c r="U211" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U211" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
@@ -27579,31 +27579,31 @@
       </c>
       <c r="Q212" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R212" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S212" s="3" t="inlineStr"/>
       <c r="T212" s="3" t="inlineStr"/>
-      <c r="U212" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U212" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
@@ -27710,31 +27710,31 @@
       </c>
       <c r="Q213" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R213" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S213" s="3" t="inlineStr"/>
       <c r="T213" s="3" t="inlineStr"/>
-      <c r="U213" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U213" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
@@ -27841,31 +27841,31 @@
       </c>
       <c r="Q214" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R214" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S214" s="3" t="inlineStr"/>
       <c r="T214" s="3" t="inlineStr"/>
-      <c r="U214" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U214" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
@@ -27972,31 +27972,31 @@
       </c>
       <c r="Q215" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R215" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S215" s="3" t="inlineStr"/>
       <c r="T215" s="3" t="inlineStr"/>
-      <c r="U215" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U215" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
@@ -28071,31 +28071,31 @@
       </c>
       <c r="Q216" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R216" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S216" s="3" t="inlineStr"/>
       <c r="T216" s="3" t="inlineStr"/>
-      <c r="U216" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U216" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
@@ -28170,31 +28170,31 @@
       </c>
       <c r="Q217" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R217" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S217" s="3" t="inlineStr"/>
       <c r="T217" s="3" t="inlineStr"/>
-      <c r="U217" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U217" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
@@ -28269,31 +28269,31 @@
       </c>
       <c r="Q218" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R218" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S218" s="3" t="inlineStr"/>
       <c r="T218" s="3" t="inlineStr"/>
-      <c r="U218" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U218" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C219" s="3" t="inlineStr">
@@ -28368,31 +28368,31 @@
       </c>
       <c r="Q219" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R219" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S219" s="3" t="inlineStr"/>
       <c r="T219" s="3" t="inlineStr"/>
-      <c r="U219" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U219" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
@@ -28499,31 +28499,31 @@
       </c>
       <c r="Q220" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R220" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S220" s="3" t="inlineStr"/>
       <c r="T220" s="3" t="inlineStr"/>
-      <c r="U220" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U220" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
@@ -28598,31 +28598,31 @@
       </c>
       <c r="Q221" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R221" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S221" s="3" t="inlineStr"/>
       <c r="T221" s="3" t="inlineStr"/>
-      <c r="U221" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U221" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
@@ -28729,31 +28729,31 @@
       </c>
       <c r="Q222" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R222" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S222" s="3" t="inlineStr"/>
       <c r="T222" s="3" t="inlineStr"/>
-      <c r="U222" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U222" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C223" s="3" t="inlineStr">
@@ -28828,31 +28828,31 @@
       </c>
       <c r="Q223" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R223" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S223" s="3" t="inlineStr"/>
       <c r="T223" s="3" t="inlineStr"/>
-      <c r="U223" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U223" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
@@ -28959,31 +28959,31 @@
       </c>
       <c r="Q224" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R224" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S224" s="3" t="inlineStr"/>
       <c r="T224" s="3" t="inlineStr"/>
-      <c r="U224" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U224" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
@@ -29058,31 +29058,31 @@
       </c>
       <c r="Q225" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R225" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S225" s="3" t="inlineStr"/>
       <c r="T225" s="3" t="inlineStr"/>
-      <c r="U225" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U225" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
@@ -29157,31 +29157,31 @@
       </c>
       <c r="Q226" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R226" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S226" s="3" t="inlineStr"/>
       <c r="T226" s="3" t="inlineStr"/>
-      <c r="U226" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U226" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29571</t>
+          <t>MCAL-30791</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
@@ -29256,123 +29256,24 @@
       </c>
       <c r="Q227" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29573</t>
+          <t>MCAL-30792</t>
         </is>
       </c>
       <c r="R227" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S227" s="3" t="inlineStr"/>
       <c r="T227" s="3" t="inlineStr"/>
-      <c r="U227" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29571</t>
-        </is>
-      </c>
-      <c r="B228" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
-        </is>
-      </c>
-      <c r="C228" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27032</t>
-        </is>
-      </c>
-      <c r="D228" s="3" t="inlineStr">
-        <is>
-          <t>Manual Test To Verify AUTOSAR 4.3.1 BSW and SPAL requirements</t>
-        </is>
-      </c>
-      <c r="E228" s="3" t="inlineStr">
-        <is>
-          <t>Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture</t>
-        </is>
-      </c>
-      <c r="F228" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-12327,MCAL-12305,MCAL-25467,MCAL-12412,MCAL-12411,MCAL-12410,MCAL-12389,MCAL-12374,MCAL-12355,MCAL-12309,MCAL-12448,MCAL-12395,MCAL-12379,MCAL-12375,MCAL-12446,MCAL-25460,MCAL-25458,MCAL-12345,MCAL-12341,MCAL-12356,MCAL-12338,MCAL-12335,MCAL-12333,MCAL-12332,MCAL-12427,MCAL-12421,MCAL-12418,MCAL-25456,MCAL-12376,MCAL-12340,MCAL-12316,MCAL-12312,MCAL-12310,MCAL-12361,MCAL-12399,MCAL-12326,MCAL-25455,MCAL-25471,MCAL-25469,MCAL-25461,MCAL-12337,MCAL-12334,MCAL-12323,MCAL-12303,MCAL-12425,MCAL-12447,MCAL-12438,MCAL-12444,MCAL-12357,MCAL-12330</t>
-        </is>
-      </c>
-      <c r="G228" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H228" s="3" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="I228" s="3" t="inlineStr">
-        <is>
-          <t>Manually verify all Modules Design requirements are satisfying the AUTOSAR BSW and SPAL requirements</t>
-        </is>
-      </c>
-      <c r="J228" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K228" s="3" t="inlineStr">
-        <is>
-          <t>Module Design requirements are satisfying the AUTOSAR BSW and SPAL requirements</t>
-        </is>
-      </c>
-      <c r="L228" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M228" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N228" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O228" s="3" t="inlineStr">
-        <is>
-          <t>Full,Sanity</t>
-        </is>
-      </c>
-      <c r="P228" s="3" t="inlineStr">
-        <is>
-          <t>Can,Dio,Gpt,Mcu,Port</t>
-        </is>
-      </c>
-      <c r="Q228" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29573</t>
-        </is>
-      </c>
-      <c r="R228" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : SPI - Manual Tests</t>
-        </is>
-      </c>
-      <c r="S228" s="3" t="inlineStr"/>
-      <c r="T228" s="3" t="inlineStr"/>
-      <c r="U228" s="10" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="U227" s="11" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U228"/>
+  <autoFilter ref="A1:U227"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/Test_Report/Spi/TestPlanExecutionReport_SPI.xlsx
+++ b/docs/Test_Report/Spi/TestPlanExecutionReport_SPI.xlsx
@@ -77,7 +77,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000000FF"/>
+        <fgColor rgb="00D3D3D3"/>
       </patternFill>
     </fill>
     <fill>
@@ -724,7 +724,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790,MCAL-30792</t>
+          <t>MCAL-32381,MCAL-32379</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09 06:41:31.972089-05:00 CDT</t>
+          <t>2025-08-29 04:27:02.810664-05:00 CDT</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>157</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>198</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>14%</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>6%</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr"/>
@@ -1730,12 +1730,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1852,12 +1852,12 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
@@ -1871,12 +1871,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1993,12 +1993,12 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr"/>
@@ -2012,12 +2012,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr"/>
@@ -2153,12 +2153,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr"/>
@@ -2284,12 +2284,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr"/>
@@ -2415,12 +2415,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr"/>
@@ -2546,12 +2546,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr"/>
@@ -2677,12 +2677,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr"/>
@@ -2808,12 +2808,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr"/>
@@ -2939,12 +2939,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr"/>
@@ -3070,12 +3070,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr"/>
@@ -3201,12 +3201,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr"/>
@@ -3332,12 +3332,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25032,MCAL-25036,MCAL-25034,MCAL-25037,MCAL-28304,MCAL-25033,MCAL-25035</t>
+          <t>MCAL-25032,MCAL-25036,MCAL-25034,MCAL-25037,MCAL-25033,MCAL-25035,MCAL-28304</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -3444,12 +3444,12 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr"/>
@@ -3463,12 +3463,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -3575,12 +3575,12 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr"/>
@@ -3594,12 +3594,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr"/>
@@ -3726,12 +3726,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr"/>
@@ -3858,12 +3858,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr"/>
@@ -3990,12 +3990,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr"/>
@@ -4122,12 +4122,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr"/>
@@ -4254,12 +4254,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr"/>
@@ -4386,12 +4386,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -4499,12 +4499,12 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
@@ -4518,12 +4518,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr"/>
@@ -4650,12 +4650,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr"/>
@@ -4782,12 +4782,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr"/>
@@ -4914,12 +4914,12 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -5027,12 +5027,12 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr"/>
@@ -5046,12 +5046,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -5159,12 +5159,12 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr"/>
@@ -5178,12 +5178,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr"/>
@@ -5309,12 +5309,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -5421,12 +5421,12 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr"/>
@@ -5440,12 +5440,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr"/>
@@ -5571,12 +5571,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr"/>
@@ -5702,12 +5702,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr"/>
@@ -5833,12 +5833,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr"/>
@@ -5964,12 +5964,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -6076,12 +6076,12 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr"/>
@@ -6095,12 +6095,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr"/>
@@ -6226,12 +6226,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-24882,MCAL-25045,MCAL-24941,MCAL-24977,MCAL-24883,MCAL-24884,MCAL-24975,MCAL-25041,MCAL-25042,MCAL-25046,MCAL-25101,MCAL-25039,MCAL-25040,MCAL-24976</t>
+          <t>MCAL-24882,MCAL-25045,MCAL-24941,MCAL-24977,MCAL-24883,MCAL-24884,MCAL-25041,MCAL-25042,MCAL-25046,MCAL-25101,MCAL-25039,MCAL-25040,MCAL-24976,MCAL-24975</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr"/>
@@ -6357,12 +6357,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr"/>
@@ -6488,12 +6488,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -6600,12 +6600,12 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr"/>
@@ -6619,12 +6619,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr"/>
@@ -6752,12 +6752,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr"/>
@@ -6885,12 +6885,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -6999,12 +6999,12 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
@@ -7018,12 +7018,12 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -7131,12 +7131,12 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr"/>
@@ -7150,12 +7150,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -7263,12 +7263,12 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr"/>
@@ -7282,12 +7282,12 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -7395,12 +7395,12 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr"/>
@@ -7414,12 +7414,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr"/>
@@ -7546,12 +7546,12 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -7659,12 +7659,12 @@
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr"/>
@@ -7678,12 +7678,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr"/>
@@ -7809,12 +7809,12 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -7921,12 +7921,12 @@
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr"/>
@@ -7940,12 +7940,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr"/>
@@ -8071,12 +8071,12 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -8183,12 +8183,12 @@
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr"/>
@@ -8202,12 +8202,12 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr"/>
@@ -8333,12 +8333,12 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr"/>
@@ -8466,12 +8466,12 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -8578,12 +8578,12 @@
       </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr"/>
@@ -8597,12 +8597,12 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr"/>
@@ -8728,12 +8728,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr"/>
@@ -8859,12 +8859,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr"/>
@@ -8990,12 +8990,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -9102,12 +9102,12 @@
       </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S58" s="3" t="inlineStr"/>
@@ -9121,12 +9121,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr"/>
@@ -9252,12 +9252,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -9365,12 +9365,12 @@
       </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr"/>
@@ -9384,12 +9384,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr"/>
@@ -9515,12 +9515,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -9627,12 +9627,12 @@
       </c>
       <c r="Q62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr"/>
@@ -9646,12 +9646,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="Q63" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R63" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S63" s="3" t="inlineStr"/>
@@ -9777,12 +9777,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -9889,12 +9889,12 @@
       </c>
       <c r="Q64" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr"/>
@@ -9908,12 +9908,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="Q65" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R65" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S65" s="3" t="inlineStr"/>
@@ -10039,12 +10039,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -10115,7 +10115,32 @@
         "port": "mcu0"
       }
     }
-  }
+  },
+"kpi_data": {
+        "track_this": true,
+        "f29h85x-evm": {
+            "c29xx_cpu1": [
+                {
+                    "text": "[SPI Performance] Sync transmission",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Elapsed time of Synchronous transmission",
+                    "group": "SPI Performance",
+                    "benchmark": 1644,
+                    "benchmark_delta": 50
+                },
+                {
+                    "text": "[SPI Performance] Async transmission",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Elapsed time of Asynchronous transmission",
+                    "group": "SPI Performance",
+                    "benchmark": 1644,
+                    "benchmark_delta": 50
+                }
+            ]
+        }
+    }
 }</t>
         </is>
       </c>
@@ -10151,12 +10176,12 @@
       </c>
       <c r="Q66" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S66" s="3" t="inlineStr"/>
@@ -10170,12 +10195,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -10246,7 +10271,41 @@
         "port": "mcu0"
       }
     }
-  }
+  },
+"kpi_data": {
+        "track_this": true,
+        "f29h85x-evm": {
+            "c29xx_cpu1": [
+                {
+                    "text": "[SPI Performance] Sync transmission time for 1024 bytes",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 1024 bytes ",
+                    "group": "SPI Performance",
+                    "benchmark": 1638,
+                    "benchmark_delta": 50
+                },
+                {
+                    "text": "[SPI Performance] Sync transmission time for 3072 bytes",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 3072 bytes ",
+                    "group": "SPI Performance",
+                    "benchmark": 4300,
+                    "benchmark_delta": 50
+                },
+                {
+                    "text": "[SPI Performance] Sync transmission time for 2048 bytes",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 2048 bytes ",
+                    "group": "SPI Performance",
+                    "benchmark": 2662,
+                    "benchmark_delta": 50
+                }
+            ]
+        }
+    }
 }</t>
         </is>
       </c>
@@ -10282,12 +10341,12 @@
       </c>
       <c r="Q67" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R67" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S67" s="3" t="inlineStr"/>
@@ -10301,12 +10360,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -10377,7 +10436,41 @@
         "port": "mcu0"
       }
     }
-  }
+  },
+"kpi_data": {
+        "track_this": true,
+        "f29h85x-evm": {
+            "c29xx_cpu1": [
+                {
+                    "text": "[SPI Performance] Async transmission time for 1024 bytes",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 1024 bytes ",
+                    "group": "SPI Performance",
+                    "benchmark": 1638,
+                    "benchmark_delta": 50
+                },
+                {
+                    "text": "[SPI Performance] Async transmission time for 3072 bytes",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 3072 bytes ",
+                    "group": "SPI Performance",
+                    "benchmark": 4300,
+                    "benchmark_delta": 50
+                },
+                {
+                    "text": "[SPI Performance] Async transmission time for 2048 bytes",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 2048 bytes ",
+                    "group": "SPI Performance",
+                    "benchmark": 2662,
+                    "benchmark_delta": 50
+                }
+            ]
+        }
+    }
 }</t>
         </is>
       </c>
@@ -10413,12 +10506,12 @@
       </c>
       <c r="Q68" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S68" s="3" t="inlineStr"/>
@@ -10432,12 +10525,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -10508,7 +10601,41 @@
         "port": "mcu0"
       }
     }
-  }
+  },
+"kpi_data": {
+        "track_this": true,
+        "f29h85x-evm": {
+            "c29xx_cpu1": [
+                {
+                    "text": "[SPI Performance] Async transmission time for 1024 bytes in Interrupt mode",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 1024 bytes ",
+                    "group": "SPI Performance",
+                    "benchmark": 1638,
+                    "benchmark_delta": 50
+                },
+                {
+                    "text": "[SPI Performance] Async transmission time for 3072 bytes in Interrupt mode",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 3072 bytes ",
+                    "group": "SPI Performance",
+                    "benchmark": 4300,
+                    "benchmark_delta": 50
+                },
+                {
+                    "text": "[SPI Performance] Async transmission time for 2048 bytes in Interrupt mode",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 2048 bytes ",
+                    "group": "SPI Performance",
+                    "benchmark": 2662,
+                    "benchmark_delta": 50
+                }
+            ]
+        }
+    }
 }</t>
         </is>
       </c>
@@ -10544,12 +10671,12 @@
       </c>
       <c r="Q69" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R69" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S69" s="3" t="inlineStr"/>
@@ -10563,12 +10690,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -10639,7 +10766,23 @@
         "port": "mcu0"
       }
     }
-  }
+  },
+"kpi_data": {
+        "track_this": true,
+        "f29h85x-evm": {
+            "c29xx_cpu1": [
+                {
+                    "text": "[Spi Performance] SPI data transmitted in 1s sync mode",
+                    "unit": "Bytes",
+                    "value_type": "int",
+                    "description": "SPI data Transmission time in Synchronous Mode for 1s",
+                    "group": "SPI Performance",
+                    "benchmark": 62640,
+                    "benchmark_delta": 1000
+                }
+            ]
+        }
+    }
 }</t>
         </is>
       </c>
@@ -10675,12 +10818,12 @@
       </c>
       <c r="Q70" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr"/>
@@ -10694,12 +10837,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -10770,7 +10913,23 @@
         "port": "mcu0"
       }
     }
-  }
+  },
+"kpi_data": {
+        "track_this": true,
+        "f29h85x-evm": {
+            "c29xx_cpu1": [
+                {
+                    "text": "[Spi Performance] SPI data transmitted in 1s async mode",
+                    "unit": "Bytes",
+                    "value_type": "int",
+                    "description": "SPI data Transmission time in Asynchronous Mode for 1second",
+                    "group": "SPI Performance",
+                    "benchmark": 62640,
+                    "benchmark_delta": 1000
+                }
+            ]
+        }
+    }
 }</t>
         </is>
       </c>
@@ -10806,12 +10965,12 @@
       </c>
       <c r="Q71" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr"/>
@@ -10825,12 +10984,12 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -10901,7 +11060,22 @@
         "port": "mcu0"
       }
     }
-  }
+  },
+"kpi_data": {
+        "f29h85x-evm": {
+            "c29xx_cpu1": [
+                {
+                    "text": "[Spi Performance] SPI data transmitted in 1s async mode",
+                    "unit": "Bytes",
+                    "value_type": "int",
+                    "description": "SPI data Transmission time in Asynchronous Mode for 1second",
+                    "group": "SPI Performance",
+                    "benchmark": 62640,
+                    "benchmark_delta": 1000
+                }
+            ]
+        }
+    }
 }</t>
         </is>
       </c>
@@ -10937,12 +11111,12 @@
       </c>
       <c r="Q72" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S72" s="3" t="inlineStr"/>
@@ -10956,12 +11130,12 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -11068,12 +11242,12 @@
       </c>
       <c r="Q73" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R73" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S73" s="3" t="inlineStr"/>
@@ -11087,12 +11261,12 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -11199,12 +11373,12 @@
       </c>
       <c r="Q74" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S74" s="3" t="inlineStr"/>
@@ -11218,12 +11392,12 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -11330,12 +11504,12 @@
       </c>
       <c r="Q75" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R75" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S75" s="3" t="inlineStr"/>
@@ -11349,12 +11523,12 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -11461,12 +11635,12 @@
       </c>
       <c r="Q76" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S76" s="3" t="inlineStr"/>
@@ -11480,12 +11654,12 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -11592,12 +11766,12 @@
       </c>
       <c r="Q77" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R77" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S77" s="3" t="inlineStr"/>
@@ -11611,12 +11785,12 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -11723,12 +11897,12 @@
       </c>
       <c r="Q78" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S78" s="3" t="inlineStr"/>
@@ -11742,12 +11916,12 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -11854,12 +12028,12 @@
       </c>
       <c r="Q79" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R79" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S79" s="3" t="inlineStr"/>
@@ -11873,12 +12047,12 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -11985,12 +12159,12 @@
       </c>
       <c r="Q80" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R80" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S80" s="3" t="inlineStr"/>
@@ -12004,12 +12178,12 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -12116,12 +12290,12 @@
       </c>
       <c r="Q81" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R81" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S81" s="3" t="inlineStr"/>
@@ -12135,12 +12309,12 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -12247,12 +12421,12 @@
       </c>
       <c r="Q82" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R82" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S82" s="3" t="inlineStr"/>
@@ -12266,12 +12440,12 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -12378,12 +12552,12 @@
       </c>
       <c r="Q83" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R83" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S83" s="3" t="inlineStr"/>
@@ -12397,12 +12571,12 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -12509,12 +12683,12 @@
       </c>
       <c r="Q84" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R84" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S84" s="3" t="inlineStr"/>
@@ -12528,12 +12702,12 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -12640,12 +12814,12 @@
       </c>
       <c r="Q85" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R85" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S85" s="3" t="inlineStr"/>
@@ -12659,12 +12833,12 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -12771,12 +12945,12 @@
       </c>
       <c r="Q86" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S86" s="3" t="inlineStr"/>
@@ -12790,12 +12964,12 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -12902,12 +13076,12 @@
       </c>
       <c r="Q87" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R87" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S87" s="3" t="inlineStr"/>
@@ -12921,12 +13095,12 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -13033,12 +13207,12 @@
       </c>
       <c r="Q88" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S88" s="3" t="inlineStr"/>
@@ -13052,12 +13226,12 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -13164,12 +13338,12 @@
       </c>
       <c r="Q89" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R89" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S89" s="3" t="inlineStr"/>
@@ -13183,12 +13357,12 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -13295,12 +13469,12 @@
       </c>
       <c r="Q90" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr"/>
@@ -13314,12 +13488,12 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -13426,12 +13600,12 @@
       </c>
       <c r="Q91" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R91" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S91" s="3" t="inlineStr"/>
@@ -13445,12 +13619,12 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -13557,12 +13731,12 @@
       </c>
       <c r="Q92" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R92" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S92" s="3" t="inlineStr"/>
@@ -13576,12 +13750,12 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -13688,12 +13862,12 @@
       </c>
       <c r="Q93" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R93" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S93" s="3" t="inlineStr"/>
@@ -13707,12 +13881,12 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -13819,12 +13993,12 @@
       </c>
       <c r="Q94" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R94" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S94" s="3" t="inlineStr"/>
@@ -13838,12 +14012,12 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -13950,12 +14124,12 @@
       </c>
       <c r="Q95" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R95" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S95" s="3" t="inlineStr"/>
@@ -13969,12 +14143,12 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -14081,12 +14255,12 @@
       </c>
       <c r="Q96" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R96" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S96" s="3" t="inlineStr"/>
@@ -14100,12 +14274,12 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -14212,12 +14386,12 @@
       </c>
       <c r="Q97" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R97" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S97" s="3" t="inlineStr"/>
@@ -14231,12 +14405,12 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -14343,12 +14517,12 @@
       </c>
       <c r="Q98" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S98" s="3" t="inlineStr"/>
@@ -14362,12 +14536,12 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -14387,7 +14561,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25053,MCAL-25049,MCAL-28318,MCAL-28336,MCAL-28342,MCAL-28348,MCAL-25064,MCAL-25056,MCAL-25063,MCAL-25055,MCAL-28356,MCAL-28593,MCAL-25062,MCAL-25052,MCAL-25048,MCAL-28323,MCAL-28330,MCAL-28335,MCAL-28353</t>
+          <t>MCAL-25053,MCAL-25049,MCAL-28318,MCAL-28336,MCAL-28342,MCAL-28348,MCAL-25064,MCAL-25056,MCAL-25063,MCAL-25055,MCAL-28356,MCAL-28593,MCAL-25062,MCAL-25052,MCAL-25048,MCAL-28353,MCAL-28323,MCAL-28330,MCAL-28335</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -14474,12 +14648,12 @@
       </c>
       <c r="Q99" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R99" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S99" s="3" t="inlineStr"/>
@@ -14493,12 +14667,12 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -14518,7 +14692,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28305,MCAL-28306,MCAL-28329,MCAL-28343,MCAL-28349,MCAL-28350,MCAL-25055,MCAL-25056,MCAL-25052,MCAL-25053,MCAL-25049,MCAL-28326,MCAL-28333,MCAL-25092,MCAL-25168,MCAL-28346,MCAL-28320,MCAL-28313,MCAL-28328,MCAL-28334,MCAL-28331,MCAL-28314,MCAL-28317,MCAL-28325,MCAL-28344,MCAL-28299,MCAL-28312,MCAL-28324,MCAL-28327,MCAL-28298,MCAL-28322,MCAL-28339,MCAL-28347,MCAL-28341,MCAL-28345,MCAL-25017,MCAL-25018,MCAL-25048,MCAL-28340,MCAL-28352,MCAL-28295,MCAL-24853,MCAL-28315,MCAL-28316,MCAL-28297,MCAL-28337,MCAL-28319,MCAL-28338</t>
+          <t>MCAL-28305,MCAL-28306,MCAL-28329,MCAL-28343,MCAL-28349,MCAL-28350,MCAL-25055,MCAL-25056,MCAL-25052,MCAL-25053,MCAL-25049,MCAL-28326,MCAL-28333,MCAL-25092,MCAL-25168,MCAL-28346,MCAL-28320,MCAL-28328,MCAL-28334,MCAL-28331,MCAL-28314,MCAL-28317,MCAL-28325,MCAL-28344,MCAL-28299,MCAL-28324,MCAL-28327,MCAL-28298,MCAL-28322,MCAL-28339,MCAL-28347,MCAL-25017,MCAL-25018,MCAL-25048,MCAL-24853,MCAL-28315,MCAL-28316,MCAL-28337,MCAL-28338,MCAL-28319,MCAL-28313,MCAL-28312,MCAL-28341,MCAL-28345,MCAL-28340,MCAL-28352,MCAL-28295,MCAL-28297</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -14605,12 +14779,12 @@
       </c>
       <c r="Q100" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R100" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S100" s="3" t="inlineStr"/>
@@ -14624,12 +14798,12 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -14736,12 +14910,12 @@
       </c>
       <c r="Q101" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R101" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S101" s="3" t="inlineStr"/>
@@ -14755,12 +14929,12 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -14868,12 +15042,12 @@
       </c>
       <c r="Q102" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R102" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S102" s="3" t="inlineStr"/>
@@ -14887,12 +15061,12 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -15000,12 +15174,12 @@
       </c>
       <c r="Q103" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R103" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S103" s="3" t="inlineStr"/>
@@ -15019,12 +15193,12 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -15132,12 +15306,12 @@
       </c>
       <c r="Q104" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R104" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S104" s="3" t="inlineStr"/>
@@ -15151,12 +15325,12 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -15176,7 +15350,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>MCAL-24993,MCAL-25173,MCAL-24994,MCAL-25070,MCAL-24952,MCAL-25161,MCAL-25182,MCAL-24995</t>
+          <t>MCAL-24993,MCAL-25173,MCAL-24994,MCAL-25070,MCAL-24952,MCAL-24995,MCAL-25182,MCAL-25161</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -15264,12 +15438,12 @@
       </c>
       <c r="Q105" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R105" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S105" s="3" t="inlineStr"/>
@@ -15283,12 +15457,12 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -15395,12 +15569,12 @@
       </c>
       <c r="Q106" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R106" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S106" s="3" t="inlineStr"/>
@@ -15414,12 +15588,12 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -15526,12 +15700,12 @@
       </c>
       <c r="Q107" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R107" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S107" s="3" t="inlineStr"/>
@@ -15545,12 +15719,12 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -15570,7 +15744,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>MCAL-24994,MCAL-28289,MCAL-28294,MCAL-28309,MCAL-28351,MCAL-25163,MCAL-24985,MCAL-25179,MCAL-24992,MCAL-24961,MCAL-28355,MCAL-25176,MCAL-28311,MCAL-28321,MCAL-28308,MCAL-28290,MCAL-28288,MCAL-24995,MCAL-25164,MCAL-28310,MCAL-28300,MCAL-28307,MCAL-28332,MCAL-28354,MCAL-28293,MCAL-25165,MCAL-25174</t>
+          <t>MCAL-24994,MCAL-28289,MCAL-28294,MCAL-28309,MCAL-28351,MCAL-25163,MCAL-24985,MCAL-25179,MCAL-24992,MCAL-24961,MCAL-28355,MCAL-25176,MCAL-28311,MCAL-28321,MCAL-28308,MCAL-28290,MCAL-28288,MCAL-24995,MCAL-25164,MCAL-28300,MCAL-28307,MCAL-28332,MCAL-28354,MCAL-28293,MCAL-25174,MCAL-25165,MCAL-28310</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -15657,12 +15831,12 @@
       </c>
       <c r="Q108" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R108" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S108" s="3" t="inlineStr"/>
@@ -15676,12 +15850,12 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -15788,12 +15962,12 @@
       </c>
       <c r="Q109" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R109" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S109" s="3" t="inlineStr"/>
@@ -15807,12 +15981,12 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -15919,12 +16093,12 @@
       </c>
       <c r="Q110" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R110" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S110" s="3" t="inlineStr"/>
@@ -15938,12 +16112,12 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -16050,12 +16224,12 @@
       </c>
       <c r="Q111" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R111" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S111" s="3" t="inlineStr"/>
@@ -16069,12 +16243,12 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -16181,12 +16355,12 @@
       </c>
       <c r="Q112" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R112" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S112" s="3" t="inlineStr"/>
@@ -16200,12 +16374,12 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -16312,12 +16486,12 @@
       </c>
       <c r="Q113" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R113" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S113" s="3" t="inlineStr"/>
@@ -16331,12 +16505,12 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -16443,12 +16617,12 @@
       </c>
       <c r="Q114" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R114" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S114" s="3" t="inlineStr"/>
@@ -16462,12 +16636,12 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -16576,12 +16750,12 @@
       </c>
       <c r="Q115" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R115" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S115" s="3" t="inlineStr"/>
@@ -16595,12 +16769,12 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -16709,12 +16883,12 @@
       </c>
       <c r="Q116" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R116" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S116" s="3" t="inlineStr"/>
@@ -16728,12 +16902,12 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -16842,12 +17016,12 @@
       </c>
       <c r="Q117" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R117" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S117" s="3" t="inlineStr"/>
@@ -16861,12 +17035,12 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -16974,12 +17148,12 @@
       </c>
       <c r="Q118" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R118" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S118" s="3" t="inlineStr"/>
@@ -16993,12 +17167,12 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -17106,12 +17280,12 @@
       </c>
       <c r="Q119" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R119" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S119" s="3" t="inlineStr"/>
@@ -17125,12 +17299,12 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -17238,12 +17412,12 @@
       </c>
       <c r="Q120" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R120" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S120" s="3" t="inlineStr"/>
@@ -17257,12 +17431,12 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -17370,12 +17544,12 @@
       </c>
       <c r="Q121" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R121" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S121" s="3" t="inlineStr"/>
@@ -17389,12 +17563,12 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -17502,12 +17676,12 @@
       </c>
       <c r="Q122" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R122" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S122" s="3" t="inlineStr"/>
@@ -17521,12 +17695,12 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -17634,12 +17808,12 @@
       </c>
       <c r="Q123" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R123" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S123" s="3" t="inlineStr"/>
@@ -17653,12 +17827,12 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -17766,12 +17940,12 @@
       </c>
       <c r="Q124" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R124" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S124" s="3" t="inlineStr"/>
@@ -17785,12 +17959,12 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -17898,12 +18072,12 @@
       </c>
       <c r="Q125" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R125" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S125" s="3" t="inlineStr"/>
@@ -17917,12 +18091,12 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -18030,12 +18204,12 @@
       </c>
       <c r="Q126" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R126" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S126" s="3" t="inlineStr"/>
@@ -18049,12 +18223,12 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -18162,12 +18336,12 @@
       </c>
       <c r="Q127" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R127" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S127" s="3" t="inlineStr"/>
@@ -18181,12 +18355,12 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -18294,12 +18468,12 @@
       </c>
       <c r="Q128" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R128" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S128" s="3" t="inlineStr"/>
@@ -18313,12 +18487,12 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -18426,12 +18600,12 @@
       </c>
       <c r="Q129" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R129" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S129" s="3" t="inlineStr"/>
@@ -18445,12 +18619,12 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -18559,12 +18733,12 @@
       </c>
       <c r="Q130" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R130" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S130" s="3" t="inlineStr"/>
@@ -18578,12 +18752,12 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -18692,12 +18866,12 @@
       </c>
       <c r="Q131" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R131" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S131" s="3" t="inlineStr"/>
@@ -18711,12 +18885,12 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -18825,12 +18999,12 @@
       </c>
       <c r="Q132" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R132" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S132" s="3" t="inlineStr"/>
@@ -18844,12 +19018,12 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -18958,12 +19132,12 @@
       </c>
       <c r="Q133" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R133" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S133" s="3" t="inlineStr"/>
@@ -18977,12 +19151,12 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -19091,12 +19265,12 @@
       </c>
       <c r="Q134" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R134" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S134" s="3" t="inlineStr"/>
@@ -19110,12 +19284,12 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -19224,12 +19398,12 @@
       </c>
       <c r="Q135" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R135" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S135" s="3" t="inlineStr"/>
@@ -19243,12 +19417,12 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -19358,12 +19532,12 @@
       </c>
       <c r="Q136" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R136" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S136" s="3" t="inlineStr"/>
@@ -19377,12 +19551,12 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
@@ -19489,12 +19663,12 @@
       </c>
       <c r="Q137" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R137" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S137" s="3" t="inlineStr"/>
@@ -19508,12 +19682,12 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
@@ -19621,12 +19795,12 @@
       </c>
       <c r="Q138" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R138" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S138" s="3" t="inlineStr"/>
@@ -19640,12 +19814,12 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30789</t>
+          <t>MCAL-32380</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -19753,12 +19927,12 @@
       </c>
       <c r="Q139" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30790</t>
+          <t>MCAL-32381</t>
         </is>
       </c>
       <c r="R139" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Automated Tests</t>
         </is>
       </c>
       <c r="S139" s="3" t="inlineStr"/>
@@ -19772,12 +19946,12 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -19852,31 +20026,31 @@
       </c>
       <c r="Q140" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R140" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S140" s="3" t="inlineStr"/>
       <c r="T140" s="3" t="inlineStr"/>
-      <c r="U140" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U140" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -19983,31 +20157,31 @@
       </c>
       <c r="Q141" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R141" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S141" s="3" t="inlineStr"/>
       <c r="T141" s="3" t="inlineStr"/>
-      <c r="U141" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U141" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -20089,31 +20263,31 @@
       </c>
       <c r="Q142" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R142" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S142" s="3" t="inlineStr"/>
       <c r="T142" s="3" t="inlineStr"/>
       <c r="U142" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
@@ -20188,31 +20362,31 @@
       </c>
       <c r="Q143" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R143" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S143" s="3" t="inlineStr"/>
       <c r="T143" s="3" t="inlineStr"/>
       <c r="U143" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -20287,31 +20461,31 @@
       </c>
       <c r="Q144" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R144" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S144" s="3" t="inlineStr"/>
       <c r="T144" s="3" t="inlineStr"/>
       <c r="U144" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
@@ -20386,31 +20560,31 @@
       </c>
       <c r="Q145" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R145" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S145" s="3" t="inlineStr"/>
       <c r="T145" s="3" t="inlineStr"/>
-      <c r="U145" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U145" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -20485,31 +20659,31 @@
       </c>
       <c r="Q146" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R146" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S146" s="3" t="inlineStr"/>
       <c r="T146" s="3" t="inlineStr"/>
-      <c r="U146" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U146" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -20584,31 +20758,31 @@
       </c>
       <c r="Q147" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R147" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S147" s="3" t="inlineStr"/>
       <c r="T147" s="3" t="inlineStr"/>
-      <c r="U147" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U147" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -20683,31 +20857,31 @@
       </c>
       <c r="Q148" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R148" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S148" s="3" t="inlineStr"/>
       <c r="T148" s="3" t="inlineStr"/>
       <c r="U148" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -20784,31 +20958,31 @@
       </c>
       <c r="Q149" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R149" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S149" s="3" t="inlineStr"/>
       <c r="T149" s="3" t="inlineStr"/>
-      <c r="U149" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U149" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -20883,31 +21057,31 @@
       </c>
       <c r="Q150" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R150" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S150" s="3" t="inlineStr"/>
       <c r="T150" s="3" t="inlineStr"/>
-      <c r="U150" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U150" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -20983,31 +21157,31 @@
       </c>
       <c r="Q151" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R151" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S151" s="3" t="inlineStr"/>
       <c r="T151" s="3" t="inlineStr"/>
-      <c r="U151" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U151" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -21084,31 +21258,31 @@
       </c>
       <c r="Q152" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R152" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S152" s="3" t="inlineStr"/>
       <c r="T152" s="3" t="inlineStr"/>
-      <c r="U152" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U152" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
@@ -21186,31 +21360,31 @@
       </c>
       <c r="Q153" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R153" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S153" s="3" t="inlineStr"/>
       <c r="T153" s="3" t="inlineStr"/>
-      <c r="U153" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U153" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -21293,31 +21467,31 @@
       </c>
       <c r="Q154" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R154" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S154" s="3" t="inlineStr"/>
       <c r="T154" s="3" t="inlineStr"/>
-      <c r="U154" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U154" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
@@ -21392,31 +21566,31 @@
       </c>
       <c r="Q155" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R155" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S155" s="3" t="inlineStr"/>
       <c r="T155" s="3" t="inlineStr"/>
-      <c r="U155" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U155" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -21491,31 +21665,31 @@
       </c>
       <c r="Q156" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R156" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S156" s="3" t="inlineStr"/>
       <c r="T156" s="3" t="inlineStr"/>
-      <c r="U156" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U156" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -21591,31 +21765,31 @@
       </c>
       <c r="Q157" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R157" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S157" s="3" t="inlineStr"/>
       <c r="T157" s="3" t="inlineStr"/>
-      <c r="U157" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U157" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -21696,31 +21870,31 @@
       </c>
       <c r="Q158" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R158" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S158" s="3" t="inlineStr"/>
       <c r="T158" s="3" t="inlineStr"/>
-      <c r="U158" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U158" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -21795,31 +21969,31 @@
       </c>
       <c r="Q159" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R159" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S159" s="3" t="inlineStr"/>
       <c r="T159" s="3" t="inlineStr"/>
-      <c r="U159" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U159" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -21890,7 +22064,50 @@
         "port": "mcu0"
       }
     }
-  }
+  },
+"kpi_data": {
+        "track_this": true,
+        "f29h85x-evm": {
+            "c29xx_cpu1": [
+                {
+                    "text": "[SPI Performance] Sync transmission time for 56000 bytes",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 56000 bytes with datawidth 8 ",
+                    "group": "SPI Performance",
+                    "benchmark": 89600,
+                    "benchmark_delta": 500
+                },
+                {
+                    "text": "[SPI Performance] Async transmission time for 56000 bytes",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 56000 bytes with datawidth 8 ",
+                    "group": "SPI Performance",
+                    "benchmark": 89600,
+                    "benchmark_delta": 500
+                },
+                {
+                    "text": "[SPI Performance] Sync transmission time for 56000 byte",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 56000 bytes with datawidth 16 ",
+                    "group": "SPI Performance",
+                    "benchmark": 179200,
+                    "benchmark_delta": 500
+                },
+                {
+                    "text": "[SPI Performance] Async transmission time for 56000 byte",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 56000 bytes with datawidth 16 ",
+                    "group": "SPI Performance",
+                    "benchmark": 179200,
+                    "benchmark_delta": 500
+                }
+            ]
+        }
+    }
 }</t>
         </is>
       </c>
@@ -21926,31 +22143,31 @@
       </c>
       <c r="Q160" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R160" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S160" s="3" t="inlineStr"/>
       <c r="T160" s="3" t="inlineStr"/>
-      <c r="U160" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U160" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -22021,7 +22238,50 @@
         "port": "mcu0"
       }
     }
-  }
+  },
+"kpi_data": {
+        "track_this": true,
+        "f29h85x-evm": {
+            "c29xx_cpu1": [
+                {
+                    "text": "[SPI Performance] Sync transmission time for 56000 bytes",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 56000 bytes with datawidth 8 ",
+                    "group": "SPI Performance",
+                    "benchmark": 44800,
+                    "benchmark_delta": 500
+                },
+                {
+                    "text": "[SPI Performance] Async transmission time for 56000 bytes",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 56000 bytes with datawidth 8 ",
+                    "group": "SPI Performance",
+                    "benchmark": 44800,
+                    "benchmark_delta": 500
+                },
+                {
+                    "text": "[SPI Performance] Sync transmission time for 56000 byte",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 56000 bytes with datawidth 16 ",
+                    "group": "SPI Performance",
+                    "benchmark": 89600,
+                    "benchmark_delta": 500
+                },
+                {
+                    "text": "[SPI Performance] Async transmission time for 56000 byte",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 56000 bytes with datawidth 16 ",
+                    "group": "SPI Performance",
+                    "benchmark": 89600,
+                    "benchmark_delta": 500
+                }
+            ]
+        }
+    }
 }</t>
         </is>
       </c>
@@ -22057,31 +22317,31 @@
       </c>
       <c r="Q161" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R161" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S161" s="3" t="inlineStr"/>
       <c r="T161" s="3" t="inlineStr"/>
-      <c r="U161" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U161" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
@@ -22152,7 +22412,50 @@
         "port": "mcu0"
       }
     }
-  }
+  },
+"kpi_data": {
+        "track_this": true,
+        "f29h85x-evm": {
+            "c29xx_cpu1": [
+                {
+                    "text": "[SPI Performance] Sync transmission time for 56000 bytes",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 56000 bytes with datawidth 8 ",
+                    "group": "SPI Performance",
+                    "benchmark": 8960,
+                    "benchmark_delta": 1000
+                },
+                {
+                    "text": "[SPI Performance] Async transmission time for 56000 bytes",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 56000 bytes with datawidth 8 ",
+                    "group": "SPI Performance",
+                    "benchmark": 8960,
+                    "benchmark_delta": 1000
+                },
+                {
+                    "text": "[SPI Performance] Sync transmission time for 56000 byte",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 56000 bytes with datawidth 16 ",
+                    "group": "SPI Performance",
+                    "benchmark": 17920,
+                    "benchmark_delta": 500
+                },
+                {
+                    "text": "[SPI Performance] Async transmission time for 56000 byte",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 56000 bytes with datawidth 16 ",
+                    "group": "SPI Performance",
+                    "benchmark": 17920,
+                    "benchmark_delta": 500
+                }
+            ]
+        }
+    }
 }</t>
         </is>
       </c>
@@ -22188,31 +22491,31 @@
       </c>
       <c r="Q162" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R162" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S162" s="3" t="inlineStr"/>
       <c r="T162" s="3" t="inlineStr"/>
-      <c r="U162" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U162" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -22283,7 +22586,50 @@
         "port": "mcu0"
       }
     }
-  }
+  },
+"kpi_data": {
+        "track_this": true,
+        "f29h85x-evm": {
+            "c29xx_cpu1": [
+                {
+                    "text": "[SPI Performance] Async transmission time for 112000 bytes",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 112000 bytes with datawidth 8 ",
+                    "group": "SPI Performance",
+                    "benchmark": 17920,
+                    "benchmark_delta": 1000
+                },
+                {
+                    "text": "[SPI Performance] Sync transmission time for 112000 bytes",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 112000 bytes with datawidth 8 ",
+                    "group": "SPI Performance",
+                    "benchmark": 17920,
+                    "benchmark_delta": 1000
+                },
+                {
+                    "text": "[SPI Performance] Async transmission time for 112000 byte",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 112000 bytes with datawidth 16 ",
+                    "group": "SPI Performance",
+                    "benchmark": 35840,
+                    "benchmark_delta": 812
+                },
+                {
+                    "text": "[SPI Performance] Sync transmission time for 112000 byte",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 112000 bytes with datawidth 16 ",
+                    "group": "SPI Performance",
+                    "benchmark": 35840,
+                    "benchmark_delta": 812
+                }
+            ]
+        }
+    }
 }</t>
         </is>
       </c>
@@ -22319,31 +22665,31 @@
       </c>
       <c r="Q163" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R163" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S163" s="3" t="inlineStr"/>
       <c r="T163" s="3" t="inlineStr"/>
-      <c r="U163" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U163" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -22414,7 +22760,50 @@
         "port": "mcu0"
       }
     }
-  }
+  },
+"kpi_data": {
+        "track_this": true,
+        "f29h85x-evm": {
+            "c29xx_cpu1": [
+                {
+                    "text": "[SPI Performance] Sync transmission time for 112000 bytes",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 112000 bytes for 8 bit ",
+                    "group": "SPI Performance",
+                    "benchmark": 89600,
+                    "benchmark_delta": 500
+                },
+                {
+                    "text": "[SPI Performance] Async transmission time for 112000 bytes",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 112000 bytes for 8 bit ",
+                    "group": "SPI Performance",
+                    "benchmark": 89600,
+                    "benchmark_delta": 500
+                },
+                {
+                    "text": "[SPI Performance] Sync transmission time for 112000 bytes",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 112000 bytes for 16 bit ",
+                    "group": "SPI Performance",
+                    "benchmark": 179200,
+                    "benchmark_delta": 500
+                },
+                {
+                    "text": "[SPI Performance] Async transmission time for 112000 bytes",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 112000 bytes for 16 bit ",
+                    "group": "SPI Performance",
+                    "benchmark": 179200,
+                    "benchmark_delta": 500
+                },
+            ]
+        }
+    }
 }</t>
         </is>
       </c>
@@ -22450,31 +22839,31 @@
       </c>
       <c r="Q164" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R164" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S164" s="3" t="inlineStr"/>
       <c r="T164" s="3" t="inlineStr"/>
-      <c r="U164" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U164" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
@@ -22545,7 +22934,50 @@
         "port": "mcu0"
       }
     }
-  }
+  },
+"kpi_data": {
+        "track_this": true,
+        "f29h85x-evm": {
+            "c29xx_cpu1": [
+                {
+                    "text": "[SPI Performance] Sync transmission time for 112000 bytes",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 112000 bytes for 8 bit ",
+                    "group": "SPI Performance",
+                    "benchmark": 179200,
+                    "benchmark_delta": 500
+                },
+                {
+                    "text": "[SPI Performance] Async transmission time for 112000 bytes",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 112000 bytes for 8 bit ",
+                    "group": "SPI Performance",
+                    "benchmark": 179200,
+                    "benchmark_delta": 500
+                },
+                {
+                    "text": "[SPI Performance] Sync transmission time for 112000 bytes",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 112000 bytes for 16 bit ",
+                    "group": "SPI Performance",
+                    "benchmark": 358400,
+                    "benchmark_delta": 500
+                },
+                {
+                    "text": "[SPI Performance] Async transmission time for 112000 bytes",
+                    "unit": "us",
+                    "value_type": "int",
+                    "description": "Transmission time for 112000 bytes for 16 bit ",
+                    "group": "SPI Performance",
+                    "benchmark": 358400,
+                    "benchmark_delta": 500
+                },
+            ]
+        }
+    }
 }</t>
         </is>
       </c>
@@ -22581,31 +23013,31 @@
       </c>
       <c r="Q165" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R165" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S165" s="3" t="inlineStr"/>
       <c r="T165" s="3" t="inlineStr"/>
-      <c r="U165" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U165" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -22680,31 +23112,31 @@
       </c>
       <c r="Q166" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R166" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S166" s="3" t="inlineStr"/>
       <c r="T166" s="3" t="inlineStr"/>
-      <c r="U166" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U166" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
@@ -22782,31 +23214,31 @@
       </c>
       <c r="Q167" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R167" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S167" s="3" t="inlineStr"/>
       <c r="T167" s="3" t="inlineStr"/>
-      <c r="U167" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U167" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -22881,31 +23313,31 @@
       </c>
       <c r="Q168" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R168" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S168" s="3" t="inlineStr"/>
       <c r="T168" s="3" t="inlineStr"/>
-      <c r="U168" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U168" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
@@ -23013,31 +23445,31 @@
       </c>
       <c r="Q169" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R169" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S169" s="3" t="inlineStr"/>
       <c r="T169" s="3" t="inlineStr"/>
       <c r="U169" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -23145,31 +23577,31 @@
       </c>
       <c r="Q170" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R170" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S170" s="3" t="inlineStr"/>
       <c r="T170" s="3" t="inlineStr"/>
       <c r="U170" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
@@ -23244,31 +23676,31 @@
       </c>
       <c r="Q171" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R171" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S171" s="3" t="inlineStr"/>
       <c r="T171" s="3" t="inlineStr"/>
-      <c r="U171" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U171" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
@@ -23375,31 +23807,31 @@
       </c>
       <c r="Q172" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R172" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S172" s="3" t="inlineStr"/>
       <c r="T172" s="3" t="inlineStr"/>
-      <c r="U172" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U172" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
@@ -23474,31 +23906,31 @@
       </c>
       <c r="Q173" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R173" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S173" s="3" t="inlineStr"/>
       <c r="T173" s="3" t="inlineStr"/>
-      <c r="U173" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U173" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
@@ -23574,31 +24006,31 @@
       </c>
       <c r="Q174" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R174" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S174" s="3" t="inlineStr"/>
       <c r="T174" s="3" t="inlineStr"/>
-      <c r="U174" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U174" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
@@ -23675,31 +24107,31 @@
       </c>
       <c r="Q175" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R175" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S175" s="3" t="inlineStr"/>
       <c r="T175" s="3" t="inlineStr"/>
-      <c r="U175" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U175" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
@@ -23775,31 +24207,31 @@
       </c>
       <c r="Q176" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R176" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S176" s="3" t="inlineStr"/>
       <c r="T176" s="3" t="inlineStr"/>
-      <c r="U176" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U176" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
@@ -23875,31 +24307,31 @@
       </c>
       <c r="Q177" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R177" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S177" s="3" t="inlineStr"/>
       <c r="T177" s="3" t="inlineStr"/>
-      <c r="U177" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U177" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -23974,31 +24406,31 @@
       </c>
       <c r="Q178" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R178" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S178" s="3" t="inlineStr"/>
       <c r="T178" s="3" t="inlineStr"/>
       <c r="U178" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
@@ -24074,31 +24506,31 @@
       </c>
       <c r="Q179" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R179" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S179" s="3" t="inlineStr"/>
       <c r="T179" s="3" t="inlineStr"/>
       <c r="U179" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
@@ -24175,31 +24607,31 @@
       </c>
       <c r="Q180" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R180" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S180" s="3" t="inlineStr"/>
       <c r="T180" s="3" t="inlineStr"/>
-      <c r="U180" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U180" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
@@ -24275,31 +24707,31 @@
       </c>
       <c r="Q181" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R181" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S181" s="3" t="inlineStr"/>
       <c r="T181" s="3" t="inlineStr"/>
-      <c r="U181" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U181" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -24374,31 +24806,31 @@
       </c>
       <c r="Q182" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R182" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S182" s="3" t="inlineStr"/>
       <c r="T182" s="3" t="inlineStr"/>
-      <c r="U182" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U182" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
@@ -24474,31 +24906,31 @@
       </c>
       <c r="Q183" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R183" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S183" s="3" t="inlineStr"/>
       <c r="T183" s="3" t="inlineStr"/>
-      <c r="U183" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U183" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -24574,31 +25006,31 @@
       </c>
       <c r="Q184" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R184" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S184" s="3" t="inlineStr"/>
       <c r="T184" s="3" t="inlineStr"/>
-      <c r="U184" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U184" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -24675,31 +25107,31 @@
       </c>
       <c r="Q185" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R185" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S185" s="3" t="inlineStr"/>
       <c r="T185" s="3" t="inlineStr"/>
-      <c r="U185" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U185" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -24776,31 +25208,31 @@
       </c>
       <c r="Q186" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R186" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S186" s="3" t="inlineStr"/>
       <c r="T186" s="3" t="inlineStr"/>
-      <c r="U186" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U186" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
@@ -24875,31 +25307,31 @@
       </c>
       <c r="Q187" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R187" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S187" s="3" t="inlineStr"/>
       <c r="T187" s="3" t="inlineStr"/>
-      <c r="U187" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U187" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
@@ -24975,31 +25407,31 @@
       </c>
       <c r="Q188" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R188" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S188" s="3" t="inlineStr"/>
       <c r="T188" s="3" t="inlineStr"/>
-      <c r="U188" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U188" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
@@ -25106,31 +25538,31 @@
       </c>
       <c r="Q189" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R189" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S189" s="3" t="inlineStr"/>
       <c r="T189" s="3" t="inlineStr"/>
-      <c r="U189" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U189" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -25206,31 +25638,31 @@
       </c>
       <c r="Q190" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R190" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S190" s="3" t="inlineStr"/>
       <c r="T190" s="3" t="inlineStr"/>
-      <c r="U190" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U190" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
@@ -25306,31 +25738,31 @@
       </c>
       <c r="Q191" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R191" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S191" s="3" t="inlineStr"/>
       <c r="T191" s="3" t="inlineStr"/>
-      <c r="U191" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U191" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -25405,31 +25837,31 @@
       </c>
       <c r="Q192" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R192" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S192" s="3" t="inlineStr"/>
       <c r="T192" s="3" t="inlineStr"/>
-      <c r="U192" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U192" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
@@ -25504,31 +25936,31 @@
       </c>
       <c r="Q193" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R193" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S193" s="3" t="inlineStr"/>
       <c r="T193" s="3" t="inlineStr"/>
-      <c r="U193" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U193" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
@@ -25603,31 +26035,31 @@
       </c>
       <c r="Q194" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R194" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S194" s="3" t="inlineStr"/>
       <c r="T194" s="3" t="inlineStr"/>
-      <c r="U194" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U194" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
@@ -25702,31 +26134,31 @@
       </c>
       <c r="Q195" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R195" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S195" s="3" t="inlineStr"/>
       <c r="T195" s="3" t="inlineStr"/>
-      <c r="U195" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U195" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
@@ -25801,31 +26233,31 @@
       </c>
       <c r="Q196" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R196" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S196" s="3" t="inlineStr"/>
       <c r="T196" s="3" t="inlineStr"/>
-      <c r="U196" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U196" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
@@ -25900,31 +26332,31 @@
       </c>
       <c r="Q197" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R197" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S197" s="3" t="inlineStr"/>
       <c r="T197" s="3" t="inlineStr"/>
-      <c r="U197" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U197" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
@@ -25999,31 +26431,31 @@
       </c>
       <c r="Q198" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R198" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S198" s="3" t="inlineStr"/>
       <c r="T198" s="3" t="inlineStr"/>
-      <c r="U198" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U198" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
@@ -26098,31 +26530,31 @@
       </c>
       <c r="Q199" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R199" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S199" s="3" t="inlineStr"/>
       <c r="T199" s="3" t="inlineStr"/>
-      <c r="U199" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U199" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
@@ -26197,31 +26629,31 @@
       </c>
       <c r="Q200" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R200" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S200" s="3" t="inlineStr"/>
       <c r="T200" s="3" t="inlineStr"/>
-      <c r="U200" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U200" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
@@ -26296,31 +26728,31 @@
       </c>
       <c r="Q201" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R201" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S201" s="3" t="inlineStr"/>
       <c r="T201" s="3" t="inlineStr"/>
-      <c r="U201" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U201" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
@@ -26395,31 +26827,31 @@
       </c>
       <c r="Q202" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R202" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S202" s="3" t="inlineStr"/>
       <c r="T202" s="3" t="inlineStr"/>
-      <c r="U202" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U202" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
@@ -26526,31 +26958,31 @@
       </c>
       <c r="Q203" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R203" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S203" s="3" t="inlineStr"/>
       <c r="T203" s="3" t="inlineStr"/>
-      <c r="U203" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U203" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
@@ -26658,31 +27090,31 @@
       </c>
       <c r="Q204" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R204" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S204" s="3" t="inlineStr"/>
       <c r="T204" s="3" t="inlineStr"/>
       <c r="U204" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
@@ -26790,31 +27222,31 @@
       </c>
       <c r="Q205" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R205" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S205" s="3" t="inlineStr"/>
       <c r="T205" s="3" t="inlineStr"/>
       <c r="U205" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
@@ -26921,31 +27353,31 @@
       </c>
       <c r="Q206" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R206" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S206" s="3" t="inlineStr"/>
       <c r="T206" s="3" t="inlineStr"/>
       <c r="U206" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
@@ -27052,31 +27484,31 @@
       </c>
       <c r="Q207" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R207" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S207" s="3" t="inlineStr"/>
       <c r="T207" s="3" t="inlineStr"/>
       <c r="U207" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
@@ -27183,31 +27615,31 @@
       </c>
       <c r="Q208" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R208" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S208" s="3" t="inlineStr"/>
       <c r="T208" s="3" t="inlineStr"/>
       <c r="U208" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
@@ -27282,31 +27714,31 @@
       </c>
       <c r="Q209" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R209" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S209" s="3" t="inlineStr"/>
       <c r="T209" s="3" t="inlineStr"/>
       <c r="U209" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
@@ -27381,31 +27813,31 @@
       </c>
       <c r="Q210" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R210" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S210" s="3" t="inlineStr"/>
       <c r="T210" s="3" t="inlineStr"/>
       <c r="U210" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
@@ -27480,31 +27912,31 @@
       </c>
       <c r="Q211" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R211" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S211" s="3" t="inlineStr"/>
       <c r="T211" s="3" t="inlineStr"/>
       <c r="U211" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
@@ -27579,31 +28011,31 @@
       </c>
       <c r="Q212" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R212" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S212" s="3" t="inlineStr"/>
       <c r="T212" s="3" t="inlineStr"/>
       <c r="U212" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
@@ -27710,31 +28142,31 @@
       </c>
       <c r="Q213" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R213" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S213" s="3" t="inlineStr"/>
       <c r="T213" s="3" t="inlineStr"/>
       <c r="U213" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
@@ -27841,31 +28273,31 @@
       </c>
       <c r="Q214" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R214" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S214" s="3" t="inlineStr"/>
       <c r="T214" s="3" t="inlineStr"/>
       <c r="U214" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
@@ -27972,31 +28404,31 @@
       </c>
       <c r="Q215" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R215" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S215" s="3" t="inlineStr"/>
       <c r="T215" s="3" t="inlineStr"/>
       <c r="U215" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
@@ -28071,31 +28503,31 @@
       </c>
       <c r="Q216" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R216" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S216" s="3" t="inlineStr"/>
       <c r="T216" s="3" t="inlineStr"/>
       <c r="U216" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
@@ -28170,31 +28602,31 @@
       </c>
       <c r="Q217" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R217" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S217" s="3" t="inlineStr"/>
       <c r="T217" s="3" t="inlineStr"/>
       <c r="U217" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
@@ -28269,31 +28701,31 @@
       </c>
       <c r="Q218" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R218" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S218" s="3" t="inlineStr"/>
       <c r="T218" s="3" t="inlineStr"/>
       <c r="U218" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C219" s="3" t="inlineStr">
@@ -28368,31 +28800,31 @@
       </c>
       <c r="Q219" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R219" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S219" s="3" t="inlineStr"/>
       <c r="T219" s="3" t="inlineStr"/>
       <c r="U219" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
@@ -28499,31 +28931,31 @@
       </c>
       <c r="Q220" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R220" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S220" s="3" t="inlineStr"/>
       <c r="T220" s="3" t="inlineStr"/>
       <c r="U220" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
@@ -28598,31 +29030,31 @@
       </c>
       <c r="Q221" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R221" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S221" s="3" t="inlineStr"/>
       <c r="T221" s="3" t="inlineStr"/>
       <c r="U221" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
@@ -28729,31 +29161,31 @@
       </c>
       <c r="Q222" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R222" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S222" s="3" t="inlineStr"/>
       <c r="T222" s="3" t="inlineStr"/>
       <c r="U222" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C223" s="3" t="inlineStr">
@@ -28828,31 +29260,31 @@
       </c>
       <c r="Q223" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R223" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S223" s="3" t="inlineStr"/>
       <c r="T223" s="3" t="inlineStr"/>
       <c r="U223" s="11" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
@@ -28959,31 +29391,31 @@
       </c>
       <c r="Q224" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R224" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S224" s="3" t="inlineStr"/>
       <c r="T224" s="3" t="inlineStr"/>
-      <c r="U224" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U224" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
@@ -29058,31 +29490,31 @@
       </c>
       <c r="Q225" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R225" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S225" s="3" t="inlineStr"/>
       <c r="T225" s="3" t="inlineStr"/>
-      <c r="U225" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U225" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
@@ -29157,31 +29589,31 @@
       </c>
       <c r="Q226" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R226" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S226" s="3" t="inlineStr"/>
       <c r="T226" s="3" t="inlineStr"/>
-      <c r="U226" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U226" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30791</t>
+          <t>MCAL-32378</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
@@ -29256,19 +29688,19 @@
       </c>
       <c r="Q227" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30792</t>
+          <t>MCAL-32379</t>
         </is>
       </c>
       <c r="R227" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : SPI - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : SPI - Manual Tests</t>
         </is>
       </c>
       <c r="S227" s="3" t="inlineStr"/>
       <c r="T227" s="3" t="inlineStr"/>
-      <c r="U227" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U227" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
